--- a/Unit_Test_Report_Traverse.xlsx
+++ b/Unit_Test_Report_Traverse.xlsx
@@ -559,7 +559,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Automated &amp; Simulated Unit API Validation Summary — Generated 2026-06-22 08:44:08</t>
+          <t>Automated &amp; Simulated Unit API Validation Summary — Generated 2026-06-22 14:08:29</t>
         </is>
       </c>
     </row>
